--- a/data/trans_dic/P3A$personadelacasa-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,93; 30,64</t>
+          <t>22,06; 31,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,4; 44,19</t>
+          <t>21,52; 43,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,83; 35,88</t>
+          <t>23,07; 36,65</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,38; 29,79</t>
+          <t>11,18; 30,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,84; 28,17</t>
+          <t>23,04; 28,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,38; 27,8</t>
+          <t>15,74; 27,85</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,43; 36,35</t>
+          <t>27,57; 36,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 28,5</t>
+          <t>9,89; 28,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 30,0</t>
+          <t>16,94; 30,36</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,45; 30,49</t>
+          <t>23,1; 30,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,93; 27,03</t>
+          <t>19,11; 27,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,47; 27,82</t>
+          <t>22,13; 27,73</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,98; 29,13</t>
+          <t>20,6; 28,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,53; 27,76</t>
+          <t>19,87; 27,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,23; 27,51</t>
+          <t>22,48; 27,55</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>139276; 194561</t>
+          <t>140079; 199580</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>155237; 320522</t>
+          <t>156112; 312227</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>310496; 488023</t>
+          <t>313766; 498509</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>147634; 355378</t>
+          <t>133360; 358109</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>218949; 270061</t>
+          <t>220884; 271239</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>352319; 598213</t>
+          <t>338625; 599304</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>193273; 256157</t>
+          <t>194309; 259888</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>110132; 266032</t>
+          <t>92286; 264913</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275840; 491415</t>
+          <t>277478; 497298</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>217149; 282407</t>
+          <t>213908; 278676</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>207075; 295608</t>
+          <t>209021; 296202</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>453932; 561838</t>
+          <t>446983; 560134</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>725812; 1007587</t>
+          <t>712530; 1001359</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>761999; 1030299</t>
+          <t>737230; 1025692</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1593901; 1972494</t>
+          <t>1611652; 1974983</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$personadelacasa-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,06; 31,43</t>
+          <t>21,27; 29,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 43,05</t>
+          <t>19,67; 25,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,07; 36,65</t>
+          <t>21,16; 26,19</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 30,02</t>
+          <t>24,63; 31,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,04; 28,29</t>
+          <t>23,17; 28,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,74; 27,85</t>
+          <t>24,62; 28,92</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,57; 36,88</t>
+          <t>26,97; 35,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,89; 28,38</t>
+          <t>24,89; 31,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,94; 30,36</t>
+          <t>26,86; 31,95</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,1; 30,09</t>
+          <t>23,67; 30,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,11; 27,08</t>
+          <t>22,8; 27,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,13; 27,73</t>
+          <t>24,02; 28,19</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,6; 28,95</t>
+          <t>25,8; 29,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,87; 27,64</t>
+          <t>24,02; 26,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,48; 27,55</t>
+          <t>25,24; 27,66</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>165961</t>
+          <t>170415</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>200082</t>
+          <t>164761</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>366043</t>
+          <t>335176</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>140079; 199580</t>
+          <t>146844; 201531</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>156112; 312227</t>
+          <t>144399; 186102</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>313766; 498509</t>
+          <t>301422; 373035</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>271931</t>
+          <t>291613</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>244987</t>
+          <t>275946</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>516918</t>
+          <t>567559</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>133360; 358109</t>
+          <t>258387; 327868</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>220884; 271239</t>
+          <t>248298; 306308</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>338625; 599304</t>
+          <t>522065; 613284</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>223641</t>
+          <t>246018</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>195372</t>
+          <t>226753</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419013</t>
+          <t>472771</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>194309; 259888</t>
+          <t>216625; 281750</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92286; 264913</t>
+          <t>202167; 255496</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>277478; 497298</t>
+          <t>433905; 516034</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>248825</t>
+          <t>266089</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>262617</t>
+          <t>281462</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>511441</t>
+          <t>547551</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>213908; 278676</t>
+          <t>234232; 301725</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>209021; 296202</t>
+          <t>254814; 310450</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>446983; 560134</t>
+          <t>506173; 593982</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>910358</t>
+          <t>974134</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>903057</t>
+          <t>948922</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1813415</t>
+          <t>1923057</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>712530; 1001359</t>
+          <t>911085; 1044348</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>737230; 1025692</t>
+          <t>897206; 1004927</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1611652; 1974983</t>
+          <t>1834414; 2009994</t>
         </is>
       </c>
     </row>
